--- a/docs/scientific/quarto-scidoc/quarto_reference_audit.xlsx
+++ b/docs/scientific/quarto-scidoc/quarto_reference_audit.xlsx
@@ -26,27 +26,39 @@
     <sheet name="anchor_links" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="other_links" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="broken_internal_links" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="broken_internal_links1" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="equations" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="missing_eq_custom_ids" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="equation_id_mismatches" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="dup_eq_custom_ids" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="dup_eq_custom_groups" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'summary'!$A$1:$B$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'all_labels'!$A$1:$F$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'all_label_refs'!$A$1:$F$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duplicate_labels'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'duplicate_label_groups'!$A$1:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'summary'!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'all_labels'!$A$1:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'all_label_refs'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duplicate_labels'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'duplicate_label_groups'!$A$1:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'missing_label_refs'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'unused_labels'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'unused_labels'!$A$1:$F$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'bib_entries'!$A$1:$E$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'bib_citations'!$A$1:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'bib_citations'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'duplicate_bib_keys'!$A$1:$F$300</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'duplicate_bib_groups'!$A$1:$C$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'missing_bib_cites'!$A$1:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'missing_bib_cites'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'missing_bib_files'!$A$1:$B$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'hyperlinks'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'hyperlinks'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'external_links'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'internal_links'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'internal_links'!$A$1:$F$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'anchor_links'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'other_links'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'broken_internal_links'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'broken_internal_links1'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'equations'!$A$1:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'missing_eq_custom_ids'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'equation_id_mismatches'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'dup_eq_custom_ids'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'dup_eq_custom_groups'!$A$1:$C$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,10 +467,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -482,7 +494,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\gmg228\Documents\RuFaS\RuFaS\docs\scientific\quarto-test</t>
+          <t>C:\Users\gmg228\Documents\RuFaS\RuFaS\docs\scientific\quarto-scidoc</t>
         </is>
       </c>
     </row>
@@ -513,7 +525,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -523,7 +535,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +555,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +575,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -583,7 +595,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -613,7 +625,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -633,7 +645,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -653,7 +665,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -694,12 +706,62 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C:\Users\gmg228\Documents\RuFaS\RuFaS\docs\scientific\quarto-test\quarto_reference_audit.xlsx</t>
-        </is>
+          <t>C:\Users\gmg228\Documents\RuFaS\RuFaS\docs\scientific\quarto-scidoc\quarto_reference_audit.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>equations_found</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>missing_equation_custom_ids</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equation_id_mismatches</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>duplicate_equation_custom_rows</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>duplicate_equation_custom_groups</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B23"/>
+  <autoFilter ref="A1:B28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10209,13 +10271,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10240,48 +10302,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>eqn-an-nrc-2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>animal.qmd</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>53</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>see @eqn-an-nrc-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>eqn-an-nrc-2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>equations.qmd</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>39</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>see @eqn-an-nrc-2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D3"/>
+  <autoFilter ref="A1:D1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10323,13 +10345,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="73" customWidth="1" min="6" max="6"/>
   </cols>
@@ -10397,10 +10419,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Animal module icon</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>resources/manure.png</t>
+          <t>resources/animal.png</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -10410,15 +10436,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>manure.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>![](resources/manure.png){width=140px}</t>
+          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
         </is>
       </c>
     </row>
@@ -10440,11 +10466,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>![](resources/manure.png){width=50%}</t>
+          <t>![](resources/manure.png){width=140px}</t>
         </is>
       </c>
     </row>
@@ -10452,60 +10478,86 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
+          <t>resources/manure.png</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>internal-file</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>manure.qmd</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>![](resources/manure.png){width=50%}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>resources/rufas.png</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>internal-file</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>index.qmd</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>![](resources/rufas.png){width=90}</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>energykey</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>energy</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>equations.qmd</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>48</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>calculation, please refer to the [energykey](energy requirements key).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10571,13 +10623,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="73" customWidth="1" min="6" max="6"/>
   </cols>
@@ -10645,10 +10697,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Animal module icon</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>resources/manure.png</t>
+          <t>resources/animal.png</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -10658,15 +10714,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>manure.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>![](resources/manure.png){width=140px}</t>
+          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
         </is>
       </c>
     </row>
@@ -10688,11 +10744,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>![](resources/manure.png){width=50%}</t>
+          <t>![](resources/manure.png){width=140px}</t>
         </is>
       </c>
     </row>
@@ -10700,30 +10756,56 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
+          <t>resources/manure.png</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>internal-file</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>manure.qmd</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>![](resources/manure.png){width=50%}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>resources/rufas.png</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>internal-file</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>index.qmd</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>![](resources/rufas.png){width=90}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10795,7 +10877,7 @@
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="72" customWidth="1" min="6" max="6"/>
   </cols>
@@ -10850,11 +10932,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>equations.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10929,15 +11011,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="73" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10975,7 +11057,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eq-energy</t>
+          <t>eq-an-nrc-1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -10985,11 +11067,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>equations.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -10998,14 +11080,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>$$ {#eq-energy}</t>
+          <t>$$ {#eq-an-nrc-1}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>eq-nrc-cbw</t>
+          <t>eq-an-nrc-2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -11015,11 +11097,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>equations.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -11028,14 +11110,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>$$CBW = MW * 0.06275$$ {#eq-nrc-cbw}</t>
+          <t>$$ {#eq-an-nrc-2}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>eq-nrc-cw</t>
+          <t>eq-an-nrc-2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -11045,11 +11127,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>equations.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -11058,14 +11140,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>$$ CW = {(18 + (DOP - 190) * 0.665) * (\frac{CBW}{45}),\text{if}DOP &gt; 190.0} $$ {#eq-nrc-cw}</t>
+          <t>$$ {#eq-an-nrc-2}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>eq-nrc-ne-maint</t>
+          <t>eq-an-nrc-2-tagged</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -11075,11 +11157,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>equations.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -11088,14 +11170,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>$$ NEmaint = 0.08 \times (BW - CW)^{0.75} $$ {#eq-nrc-ne-maint}</t>
+          <t>$$ {#eq-an-nrc-2-tagged}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>eq-nutrient-proportion</t>
+          <t>eq-an-nrc-3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -11105,11 +11187,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>equations.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -11118,19 +11200,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>$$ {#eq-nutrient-proportion}</t>
+          <t>$$ {#eq-an-nrc-3}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fig-animal-icon</t>
+          <t>eq-an-nrc-4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -11139,7 +11221,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -11148,19 +11230,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
+          <t>$$ {#eq-an-nrc-4}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-1</t>
+          <t>eq-an-nrc-5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -11169,7 +11251,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -11178,19 +11260,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-1}</t>
+          <t>$$ {#eq-an-nrc-5}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-2</t>
+          <t>eq-an-nrc-6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -11199,7 +11281,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -11208,28 +11290,28 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-2}</t>
+          <t>$$ {#eq-an-nrc-6}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-2</t>
+          <t>eq-an-nrc-6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -11238,28 +11320,28 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-2}</t>
+          <t>$$ {#eq-an-nrc-6}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-2</t>
+          <t>eq-energy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>equations.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -11268,28 +11350,28 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-2}</t>
+          <t>$$ {#eq-energy}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-3</t>
+          <t>eq-nrc-cbw</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -11298,28 +11380,28 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-3}</t>
+          <t>$$ {#eq-nrc-cbw}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-4</t>
+          <t>eq-nrc-cbw-times</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -11328,28 +11410,28 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-4}</t>
+          <t>$$ {#eq-nrc-cbw-times}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-5</t>
+          <t>eq-nrc-cw</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -11358,28 +11440,28 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-5}</t>
+          <t>$$ {#eq-nrc-cw}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sec-nrc</t>
+          <t>eq-nrc-ne-maint</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Section</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>equations.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -11388,28 +11470,28 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>## Nutrient Requirements of Dairy Cattle (NRC) {#sec-nrc}</t>
+          <t>$$ {#eq-nrc-ne-maint}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tbl-animal-inputs</t>
+          <t>eq-nutrient-proportion</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -11418,42 +11500,1595 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+          <t>$$ {#eq-nutrient-proportion}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>fig-animal-icon</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fig-animal-icon</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>17</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sec-nrc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>45</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>## Nutrient Requirements of Dairy Cattle (NRC) {#sec-nrc}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>tbl-animal-inputs</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Table</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>18</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tbl-animal-inputs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>tbl-animal-inputs</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>manure.qmd</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D22" t="n">
         <v>26</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>attribute-id</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>: Example animal inputs {#tbl-animal-inputs}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F17"/>
+  <autoFilter ref="A1:F22"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>link_text</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>resolved_path</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>eq_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>custom_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>expected_custom_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>matches_expected</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>has_custom_id</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>equation_body</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AN.NRC.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AN.NRC.2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.2)}</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AN.NRC.3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AN.NRC.3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>26</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.3)}</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AN.NRC.4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AN.NRC.4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.4)}</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AN.NRC.5</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AN.NRC.5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>34</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.5)}</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AN.NRC.1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AN.NRC.1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>38</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.1)}</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AN.NRC.6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AN.NRC.6</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>42</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.6)}</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AN.NRC.2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AN.NRC.2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>29</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.2)}</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AN.NRC.6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AN.NRC.6</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>33</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.6)}</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>eq-nrc-cbw</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NRC.CBW</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>54</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>eq-nrc-cw</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NRC.CW</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>58</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CW = {(18 + (DOP - 190) * 0.665) * \left(\frac{CBW}{45}\right), \text{if } DOP &gt; 190.0}</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>eq-nrc-ne-maint</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NRC.NE.MAINT</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>64</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NEmaint = 0.08 \times (BW - CW)^{0.75}</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>eq-nrc-cbw-times</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NRC.CBW.TIMES</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>73</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>CBW = MW \times 0.06275</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-2-tagged</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AN.NRC.2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AN.NRC.2.TAGGED</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>84</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275 \tag{AN.NRC.2}</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>eq-energy</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>94</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>E = mc^2</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>eq-nutrient-proportion</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NUTRIENT.PROPORTION</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>\text{nutrient\_proportion\_to\_be\_removed} = \min\left( \frac{\text{mass\_requested\_nutrient}}{\text{manure\_nutrient\_available}}, 1 \right)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I16"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>eq_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>expected_custom_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>equation_body</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>eq-nrc-cbw</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NRC.CBW</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>54</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>eq-nrc-cw</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NRC.CW</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>58</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CW = {(18 + (DOP - 190) * 0.665) * \left(\frac{CBW}{45}\right), \text{if } DOP &gt; 190.0}</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>eq-nrc-ne-maint</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NRC.NE.MAINT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>64</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NEmaint = 0.08 \times (BW - CW)^{0.75}</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>eq-nrc-cbw-times</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NRC.CBW.TIMES</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>73</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CBW = MW \times 0.06275</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>eq-energy</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>94</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>E = mc^2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>eq-nutrient-proportion</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NUTRIENT.PROPORTION</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>\text{nutrient\_proportion\_to\_be\_removed} = \min\left( \frac{\text{mass\_requested\_nutrient}}{\text{manure\_nutrient\_available}}, 1 \right)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>eq_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>custom_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>expected_custom_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>equation_body</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-2-tagged</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AN.NRC.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AN.NRC.2.TAGGED</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>84</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275 \tag{AN.NRC.2}</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>custom_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>eq_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>equation_body</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AN.NRC.2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.2)}</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AN.NRC.2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.2)}</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AN.NRC.2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-2-tagged</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>84</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275 \tag{AN.NRC.2}</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AN.NRC.6</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>42</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.6)}</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AN.NRC.6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-6</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>33</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.6)}</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>$$</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>custom_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AN.NRC.2</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>animal.qmd; example_structures.qmd</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AN.NRC.6</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>animal.qmd; example_structures.qmd</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11464,12 +13099,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="66" customWidth="1" min="6" max="6"/>
@@ -11510,7 +13145,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eq-energy</t>
+          <t>eq-an-nrc-2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11520,11 +13155,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>equations.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -11533,42 +13168,132 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>See Equation @eq-energy.</t>
+          <t>See @eq-an-nrc-2.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>eq-an-nrc-2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>37</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>@id</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>See @eq-an-nrc-2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-2-tagged</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>88</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>@id</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>See @eq-an-nrc-2-tagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>eq-energy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>98</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>@id</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>See Equation @eq-energy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>eq-nrc-cbw</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>equations.qmd</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>23</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>70</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>@id</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>@eq-nrc-cbw may be visually improved by using the `\times` LaTeX</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F3"/>
+  <autoFilter ref="A1:F6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11579,15 +13304,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="73" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -11631,12 +13356,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-2</t>
+          <t>eq-an-nrc-2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -11645,7 +13370,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -11654,31 +13379,31 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-2}</t>
+          <t>$$ {#eq-an-nrc-2}</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-2</t>
+          <t>eq-an-nrc-2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -11687,31 +13412,31 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-2}</t>
+          <t>$$ {#eq-an-nrc-2}</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-2</t>
+          <t>eq-an-nrc-6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>equations.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -11720,31 +13445,31 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-2}</t>
+          <t>$$ {#eq-an-nrc-6}</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tbl-animal-inputs</t>
+          <t>eq-an-nrc-6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -11753,7 +13478,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+          <t>$$ {#eq-an-nrc-6}</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -11763,21 +13488,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tbl-animal-inputs</t>
+          <t>fig-animal-icon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>manure.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -11786,15 +13511,147 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>fig-animal-icon</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>17</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tbl-animal-inputs</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tbl-animal-inputs</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>25</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tbl-animal-inputs</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>manure.qmd</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>26</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11805,13 +13662,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11839,32 +13696,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-2</t>
+          <t>eq-an-nrc-2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>animal.qmd; equations.qmd</t>
+          <t>animal.qmd; example_structures.qmd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tbl-animal-inputs</t>
+          <t>eq-an-nrc-6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -11872,12 +13729,52 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>animal.qmd; manure.qmd</t>
+          <t>animal.qmd; example_structures.qmd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>fig-animal-icon</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>animal.qmd; example_structures.qmd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tbl-animal-inputs</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>animal.qmd; example_structures.qmd; manure.qmd</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D3"/>
+  <autoFilter ref="A1:D5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11943,15 +13840,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="73" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11989,7 +13886,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eq-nrc-cw</t>
+          <t>eq-an-nrc-1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11999,11 +13896,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>equations.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -12012,14 +13909,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>$$ CW = {(18 + (DOP - 190) * 0.665) * (\frac{CBW}{45}),\text{if}DOP &gt; 190.0} $$ {#eq-nrc-cw}</t>
+          <t>$$ {#eq-an-nrc-1}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>eq-nrc-ne-maint</t>
+          <t>eq-an-nrc-3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12029,11 +13926,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>equations.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -12042,14 +13939,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>$$ NEmaint = 0.08 \times (BW - CW)^{0.75} $$ {#eq-nrc-ne-maint}</t>
+          <t>$$ {#eq-an-nrc-3}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>eq-nutrient-proportion</t>
+          <t>eq-an-nrc-4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12059,11 +13956,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>equations.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -12072,19 +13969,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>$$ {#eq-nutrient-proportion}</t>
+          <t>$$ {#eq-an-nrc-4}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-1</t>
+          <t>eq-an-nrc-5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -12093,7 +13990,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -12102,19 +13999,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-1}</t>
+          <t>$$ {#eq-an-nrc-5}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-2</t>
+          <t>eq-an-nrc-6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -12123,7 +14020,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -12132,28 +14029,28 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-2}</t>
+          <t>$$ {#eq-an-nrc-6}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-2</t>
+          <t>eq-an-nrc-6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -12162,28 +14059,28 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-2}</t>
+          <t>$$ {#eq-an-nrc-6}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-2</t>
+          <t>eq-nrc-cbw-times</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>equations.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -12192,28 +14089,28 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-2}</t>
+          <t>$$ {#eq-nrc-cbw-times}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-3</t>
+          <t>eq-nrc-cw</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -12222,28 +14119,28 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-3}</t>
+          <t>$$ {#eq-nrc-cw}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-4</t>
+          <t>eq-nrc-ne-maint</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -12252,28 +14149,28 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-4}</t>
+          <t>$$ {#eq-nrc-ne-maint}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>eqn-an-nrc-5</t>
+          <t>eq-nutrient-proportion</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Equation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -12282,7 +14179,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>:::{#eqn-an-nrc-5}</t>
+          <t>$$ {#eq-nutrient-proportion}</t>
         </is>
       </c>
     </row>
@@ -12319,21 +14216,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sec-nrc</t>
+          <t>fig-animal-icon</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Section</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>equations.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -12342,28 +14239,28 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>## Nutrient Requirements of Dairy Cattle (NRC) {#sec-nrc}</t>
+          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tbl-animal-inputs</t>
+          <t>sec-nrc</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -12372,7 +14269,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+          <t>## Nutrient Requirements of Dairy Cattle (NRC) {#sec-nrc}</t>
         </is>
       </c>
     </row>
@@ -12389,25 +14286,85 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>18</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tbl-animal-inputs</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tbl-animal-inputs</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>manure.qmd</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D17" t="n">
         <v>26</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>attribute-id</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>: Example animal inputs {#tbl-animal-inputs}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F15"/>
+  <autoFilter ref="A1:F17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19942,13 +21899,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19973,48 +21930,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>eqn-an-nrc-2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>animal.qmd</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>53</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>see @eqn-an-nrc-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>eqn-an-nrc-2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>equations.qmd</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>39</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>see @eqn-an-nrc-2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D3"/>
+  <autoFilter ref="A1:D1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/scientific/quarto-scidoc/quarto_reference_audit.xlsx
+++ b/docs/scientific/quarto-scidoc/quarto_reference_audit.xlsx
@@ -35,30 +35,30 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'summary'!$A$1:$B$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'all_labels'!$A$1:$F$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'all_label_refs'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'all_labels'!$A$1:$F$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'all_label_refs'!$A$1:$F$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duplicate_labels'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'duplicate_label_groups'!$A$1:$D$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'missing_label_refs'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'unused_labels'!$A$1:$F$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'missing_label_refs'!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'unused_labels'!$A$1:$F$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'bib_entries'!$A$1:$E$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'bib_citations'!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'duplicate_bib_keys'!$A$1:$F$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'bib_citations'!$A$1:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'duplicate_bib_keys'!$A$1:$F$296</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'duplicate_bib_groups'!$A$1:$C$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'missing_bib_cites'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'missing_bib_cites'!$A$1:$D$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'missing_bib_files'!$A$1:$B$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'hyperlinks'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'hyperlinks'!$A$1:$F$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'external_links'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'internal_links'!$A$1:$F$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'anchor_links'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'internal_links'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'anchor_links'!$A$1:$F$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'other_links'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'broken_internal_links'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'broken_internal_links1'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'equations'!$A$1:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'missing_eq_custom_ids'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'equation_id_mismatches'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'dup_eq_custom_ids'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'dup_eq_custom_groups'!$A$1:$C$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'dup_eq_custom_ids'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'dup_eq_custom_groups'!$A$1:$C$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F300"/>
+  <dimension ref="A1:F296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -3164,13 +3164,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Li2022</t>
+          <t>Li2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3180,15 +3180,15 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>565</v>
+        <v>523</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>pages   = {2681-2693}</t>
+          <t>@article{Li2023,</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3208,11 +3208,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>523</v>
+        <v>621</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3236,11 +3236,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>621</v>
+        <v>499</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3264,11 +3264,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>499</v>
+        <v>557</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3292,15 +3292,15 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>557</v>
+        <v>576</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>@article{Li2023,</t>
+          <t>pages   = {7525–7538}</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3310,7 +3310,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Li2023</t>
+          <t>Mills2003</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3320,15 +3320,15 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>576</v>
+        <v>329</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>pages   = {7525–7538}</t>
+          <t>note      = {Accessed 2025-04-17}</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3348,11 +3348,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>329</v>
+        <v>427</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3376,11 +3376,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>427</v>
+        <v>305</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3404,11 +3404,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>305</v>
+        <v>363</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3432,11 +3432,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Mills2003</t>
+          <t>Moraes2014</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3460,15 +3460,15 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>356</v>
+        <v>300</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>note      = {Accessed 2025-04-17}</t>
+          <t>doi       = {10.5713/ajas.2003.1443}</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3488,11 +3488,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>300</v>
+        <v>398</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3516,11 +3516,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>398</v>
+        <v>276</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3544,11 +3544,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>276</v>
+        <v>334</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3572,11 +3572,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3590,25 +3590,25 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Moraes2014</t>
+          <t>Mukhtar1999</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>techreport</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>324</v>
+        <v>197</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>doi       = {10.5713/ajas.2003.1443}</t>
+          <t>doi = {10.1016/j.biortech.2009.01.056}</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3628,11 +3628,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>197</v>
+        <v>295</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3656,11 +3656,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>295</v>
+        <v>173</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3684,11 +3684,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>173</v>
+        <v>231</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3712,11 +3712,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3730,25 +3730,25 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Mukhtar1999</t>
+          <t>NRCS2017</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>techreport</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>212</v>
+        <v>65</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>doi = {10.1016/j.biortech.2009.01.056}</t>
+          <t>note   = {Accessed: 2024-05-17}</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3768,11 +3768,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3796,11 +3796,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>163</v>
+        <v>41</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3824,11 +3824,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3852,11 +3852,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3870,25 +3870,25 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>NRCS2017</t>
+          <t>Niu2018</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>69</v>
+        <v>311</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>note   = {Accessed: 2024-05-17}</t>
+          <t>doi       = {10.1111/gcb.12471}</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3908,11 +3908,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>311</v>
+        <v>409</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3936,11 +3936,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>409</v>
+        <v>287</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3964,11 +3964,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>287</v>
+        <v>345</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3992,11 +3992,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Niu2018</t>
+          <t>Pattanaik2003</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4020,15 +4020,15 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>336</v>
+        <v>289</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>doi       = {10.1111/gcb.12471}</t>
+          <t>pmcid     = {PMC9868067}</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -4048,11 +4048,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>289</v>
+        <v>387</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4076,11 +4076,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>387</v>
+        <v>265</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4104,11 +4104,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>265</v>
+        <v>323</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4132,11 +4132,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Pattanaik2003</t>
+          <t>Petersen2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4160,15 +4160,15 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>312</v>
+        <v>95</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>pmcid     = {PMC9868067}</t>
+          <t>url     = {https://link.springer.com/article/10.1023/b:fres.0000029678.25083.fa}</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -4188,11 +4188,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4216,11 +4216,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>193</v>
+        <v>71</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4244,11 +4244,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4272,11 +4272,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Petersen2024</t>
+          <t>Rotz2006</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4300,15 +4300,15 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>url     = {https://link.springer.com/article/10.1023/b:fres.0000029678.25083.fa}</t>
+          <t>note   = {Accessed: 2024-05-17}</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -4328,11 +4328,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4356,11 +4356,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>171</v>
+        <v>49</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4384,11 +4384,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4412,11 +4412,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4430,25 +4430,25 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Rotz2006</t>
+          <t>Rotz2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>techreport</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>78</v>
+        <v>246</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>note   = {Accessed: 2024-05-17}</t>
+          <t>pages = {1301--1312}</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -4468,11 +4468,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>246</v>
+        <v>344</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4496,11 +4496,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>344</v>
+        <v>222</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4524,11 +4524,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>222</v>
+        <v>280</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4552,11 +4552,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4570,25 +4570,25 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Rotz2023</t>
+          <t>Sommer2004</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>techreport</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>266</v>
+        <v>84</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>pages = {1301--1312}</t>
+          <t>url     = {https://elibrary.asabe.org/abstract.asp?aid=21731&amp;t=2&amp;redir=&amp;redirType=}</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -4608,11 +4608,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>84</v>
+        <v>182</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4636,11 +4636,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4664,11 +4664,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4692,11 +4692,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sommer2004</t>
+          <t>Sommer2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4720,15 +4720,15 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>url     = {https://elibrary.asabe.org/abstract.asp?aid=21731&amp;t=2&amp;redir=&amp;redirType=}</t>
+          <t>url     = {https://www.sciencedirect.com/science/article/pii/S0048969715304861}</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -4748,11 +4748,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>125</v>
+        <v>223</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4776,11 +4776,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>223</v>
+        <v>101</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4804,11 +4804,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>101</v>
+        <v>159</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4832,11 +4832,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sommer2022</t>
+          <t>Varma2021</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4860,15 +4860,15 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>135</v>
+        <v>205</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>url     = {https://www.sciencedirect.com/science/article/pii/S0048969715304861}</t>
+          <t>note = {Publication L-5340}</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -4888,11 +4888,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>205</v>
+        <v>303</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4916,11 +4916,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>303</v>
+        <v>181</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4944,11 +4944,11 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>181</v>
+        <v>239</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4972,11 +4972,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Varma2021</t>
+          <t>Wood1967</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5000,15 +5000,15 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>221</v>
+        <v>453</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>note = {Publication L-5340}</t>
+          <t>pages = {324--332}</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -5028,11 +5028,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>453</v>
+        <v>551</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5056,11 +5056,11 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>551</v>
+        <v>429</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5084,11 +5084,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>429</v>
+        <v>487</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5112,11 +5112,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Wood1967</t>
+          <t>appuhamy2014</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5140,15 +5140,15 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>491</v>
+        <v>340</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>pages = {324--332}</t>
+          <t>doi       = {10.2527/2003.81123141x}</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -5168,11 +5168,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>340</v>
+        <v>438</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5196,11 +5196,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>438</v>
+        <v>316</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5224,11 +5224,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>316</v>
+        <v>374</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5252,11 +5252,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>appuhamy2014</t>
+          <t>appuhamy2018</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5280,15 +5280,15 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>doi       = {10.2527/2003.81123141x}</t>
+          <t>number = {12}</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -5308,11 +5308,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>349</v>
+        <v>447</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5336,11 +5336,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>447</v>
+        <v>325</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5364,11 +5364,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>325</v>
+        <v>383</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5392,11 +5392,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5410,25 +5410,25 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>appuhamy2018</t>
+          <t>asabe2005</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>book</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>number = {12}</t>
+          <t>pages = {820--829}</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -5448,11 +5448,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>359</v>
+        <v>457</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5476,11 +5476,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>457</v>
+        <v>335</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5504,11 +5504,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>335</v>
+        <v>393</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5532,11 +5532,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5550,25 +5550,25 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>asabe2005</t>
+          <t>bannink1999</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>pages = {820--829}</t>
+          <t>pages = {1--32}</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -5588,11 +5588,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>368</v>
+        <v>466</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5616,11 +5616,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>466</v>
+        <v>344</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5644,11 +5644,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>344</v>
+        <v>402</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5672,11 +5672,11 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>bannink1999</t>
+          <t>boadi2004</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5700,15 +5700,15 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>pages = {1--32}</t>
+          <t>pages = {1008--1018}</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -5728,11 +5728,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>377</v>
+        <v>475</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5756,11 +5756,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>475</v>
+        <v>353</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5784,11 +5784,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>353</v>
+        <v>411</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5812,11 +5812,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>boadi2004</t>
+          <t>bonifacio2017a</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5840,15 +5840,15 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>409</v>
+        <v>24</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>pages = {1008--1018}</t>
+          <t>year      = {1997}</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -5868,15 +5868,15 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>year      = {1997}</t>
+          <t>note      = {\url{http://ww2.arb.ca.gov/sites/default/files/classic/research/apr/past/16rd002.pdf}},</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -5896,15 +5896,15 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>note      = {\url{http://ww2.arb.ca.gov/sites/default/files/classic/research/apr/past/16rd002.pdf}},</t>
+          <t>@article{bonifacio2017a,</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -5924,15 +5924,15 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>@article{bonifacio2017a,</t>
+          <t>note      = {\url{http://ww2.arb.ca.gov/sites/default/files/classic/research/apr/past/16rd002.pdf}},</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -5952,15 +5952,15 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>note      = {\url{http://ww2.arb.ca.gov/sites/default/files/classic/research/apr/past/16rd002.pdf}},</t>
+          <t>year      = {1997}</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -5970,7 +5970,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>bonifacio2017a</t>
+          <t>bonifacio2017b</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5980,15 +5980,15 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>year      = {1997}</t>
+          <t>number    = {3}</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -6008,11 +6008,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6036,11 +6036,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6064,11 +6064,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6092,11 +6092,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6110,29 +6110,29 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>bonifacio2017b</t>
+          <t>dcrc_protocols</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>number    = {3}</t>
+          <t>@misc{dcrc_protocols,</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>@misc{dcrc_protocols,</t>
+          <t>publisher={The University of Wisconsin-Madison}</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -6166,29 +6166,29 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>dcrc_protocols</t>
+          <t>deboer2002a</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>7</v>
+        <v>388</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>publisher={The University of Wisconsin-Madison}</t>
+          <t>doi = {10.4141/A03-109}</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194">
@@ -6204,11 +6204,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>388</v>
+        <v>486</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6232,11 +6232,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>486</v>
+        <v>364</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6260,11 +6260,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>364</v>
+        <v>422</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6288,11 +6288,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>deboer2002a</t>
+          <t>devries2006</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6316,15 +6316,15 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>421</v>
+        <v>487</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>doi = {10.4141/A03-109}</t>
+          <t>@article{devries2006,</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -6344,11 +6344,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>487</v>
+        <v>585</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6372,11 +6372,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>585</v>
+        <v>463</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6400,11 +6400,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>463</v>
+        <v>521</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6428,15 +6428,15 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>@article{devries2006,</t>
+          <t>pages   = {239-253}</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -6446,7 +6446,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>devries2006</t>
+          <t>endres2007behavior</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6456,19 +6456,19 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>532</v>
+        <v>73</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>pages   = {239-253}</t>
+          <t>number      = {Technical Report No. 406}</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -6484,15 +6484,15 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>number      = {Technical Report No. 406}</t>
+          <t>note         = {Accessed: 2023-06-20}</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -6512,15 +6512,15 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>9</v>
+        <v>681</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>note         = {Accessed: 2023-06-20}</t>
+          <t>number      = {Technical Report No. 406}</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -6530,7 +6530,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>endres2007behavior</t>
+          <t>espejo2007herd</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6540,15 +6540,15 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>681</v>
+        <v>82</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>number      = {Technical Report No. 406}</t>
+          <t>pages     = {4192--4200},</t>
         </is>
       </c>
       <c r="F206" t="n">
@@ -6568,11 +6568,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6596,11 +6596,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>18</v>
+        <v>691</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>espejo2007herd</t>
+          <t>fan2016root</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6624,19 +6624,19 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>691</v>
+        <v>54</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>pages     = {4192--4200},</t>
+          <t>year         = {2022},</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -6652,11 +6652,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>54</v>
+        <v>660</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>fan2016root</t>
+          <t>gomez2010time</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6680,19 +6680,19 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>660</v>
+        <v>93</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>year         = {2022},</t>
+          <t>doi       = {10.3168/jds.S0022-0302(07)72631-0},</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212">
@@ -6708,11 +6708,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6736,11 +6736,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>29</v>
+        <v>703</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>gomez2010time</t>
+          <t>hargreaves1985</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6764,19 +6764,19 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>703</v>
+        <v>1</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>doi       = {10.3168/jds.S0022-0302(07)72631-0},</t>
+          <t>@article{hargreaves1985,</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215">
@@ -6792,15 +6792,15 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1</v>
+        <v>595</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>@article{hargreaves1985,</t>
+          <t>year = {2017}</t>
         </is>
       </c>
       <c r="F215" t="n">
@@ -6810,7 +6810,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>hargreaves1985</t>
+          <t>hayes2020vindication</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6820,15 +6820,15 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>595</v>
+        <v>37</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>year = {2017}</t>
+          <t>@article{hayes2020vindication,</t>
         </is>
       </c>
       <c r="F216" t="n">
@@ -6848,15 +6848,15 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>37</v>
+        <v>639</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>@article{hayes2020vindication,</t>
+          <t>institution={Texas Water Resources Institute}</t>
         </is>
       </c>
       <c r="F217" t="n">
@@ -6866,7 +6866,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>hayes2020vindication</t>
+          <t>jewell2019prevalence</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6876,19 +6876,19 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>639</v>
+        <v>104</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>institution={Texas Water Resources Institute}</t>
+          <t>doi       = {10.3168/jds.2010-3436},</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219">
@@ -6904,11 +6904,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -6932,11 +6932,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>40</v>
+        <v>715</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>jewell2019prevalence</t>
+          <t>johnson2016</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6960,19 +6960,19 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>715</v>
+        <v>399</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>doi       = {10.3168/jds.2010-3436},</t>
+          <t>doi = {10.3168/jds.S0022-0302(02)74425-1}</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222">
@@ -6988,11 +6988,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>399</v>
+        <v>497</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7016,11 +7016,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>497</v>
+        <v>375</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7044,11 +7044,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>375</v>
+        <v>433</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -7090,29 +7090,29 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>johnson2016</t>
+          <t>kalantari2015using</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>book</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>433</v>
+        <v>1</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>doi = {10.3168/jds.S0022-0302(02)74425-1}</t>
+          <t>@book{kalantari2015using,</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -7146,29 +7146,29 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>kalantari2015using</t>
+          <t>larney2011</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>@book{kalantari2015using,</t>
+          <t>number    = {3}</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229">
@@ -7184,11 +7184,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7212,11 +7212,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>142</v>
+        <v>20</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7240,11 +7240,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7268,11 +7268,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>larney2011</t>
+          <t>mcelroy1977nitrogen</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7296,19 +7296,19 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>number    = {3}</t>
+          <t>@article{mcelroy1977nitrogen,</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -7324,15 +7324,15 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>21</v>
+        <v>619</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>@article{mcelroy1977nitrogen,</t>
+          <t>publisher={Wiley Online Library}</t>
         </is>
       </c>
       <c r="F234" t="n">
@@ -7342,29 +7342,29 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>mcelroy1977nitrogen</t>
+          <t>meyer2019contract</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>techreport</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>619</v>
+        <v>114</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>publisher={Wiley Online Library}</t>
+          <t>pages     = {3392--3405},</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -7380,11 +7380,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7408,11 +7408,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>50</v>
+        <v>726</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -7426,29 +7426,29 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>meyer2019contract</t>
+          <t>monteny2002b</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>techreport</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>726</v>
+        <v>410</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>pages     = {3392--3405},</t>
+          <t>doi = {10.3168/jds.2015-10730}</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239">
@@ -7464,11 +7464,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>410</v>
+        <v>508</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -7492,11 +7492,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>508</v>
+        <v>386</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -7520,11 +7520,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -7548,11 +7548,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -7566,29 +7566,29 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>monteny2002b</t>
+          <t>mu-extsoil</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>445</v>
+        <v>46</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>doi = {10.3168/jds.2015-10730}</t>
+          <t>@misc{mu-extsoil,</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -7604,15 +7604,15 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>46</v>
+        <v>650</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>@misc{mu-extsoil,</t>
+          <t>publisher={Elsevier}</t>
         </is>
       </c>
       <c r="F244" t="n">
@@ -7622,29 +7622,29 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>mu-extsoil</t>
+          <t>muck2013recent</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>650</v>
+        <v>265</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>publisher={Elsevier}</t>
+          <t>pages     = {31--93}</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246">
@@ -7660,11 +7660,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>265</v>
+        <v>363</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -7688,11 +7688,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>363</v>
+        <v>241</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -7716,11 +7716,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>241</v>
+        <v>299</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -7744,11 +7744,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -7762,29 +7762,29 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>muck2013recent</t>
+          <t>neitsch2011swat</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>techreport</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>286</v>
+        <v>65</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>pages     = {31--93}</t>
+          <t>url       = {https://doi.org/10.1016/j.fcr.2016.02.013}</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -7800,11 +7800,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>65</v>
+        <v>672</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -7818,29 +7818,29 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>neitsch2011swat</t>
+          <t>nennich2005</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>techreport</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>672</v>
+        <v>421</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>url       = {https://doi.org/10.1016/j.fcr.2016.02.013}</t>
+          <t>doi = {10.3168/jds.S0022-0302(02)74426-3}</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253">
@@ -7856,11 +7856,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>421</v>
+        <v>519</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -7884,11 +7884,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>519</v>
+        <v>397</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -7912,11 +7912,11 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>397</v>
+        <v>455</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -7940,11 +7940,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -7958,29 +7958,29 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>nennich2005</t>
+          <t>nrc2001</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>book</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>doi = {10.3168/jds.S0022-0302(02)74426-3}</t>
+          <t>@book{nrc2001,</t>
         </is>
       </c>
       <c r="F257" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="258">
@@ -7996,11 +7996,11 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>471</v>
+        <v>569</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="259">
@@ -8024,11 +8024,11 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>569</v>
+        <v>447</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="260">
@@ -8052,11 +8052,11 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>447</v>
+        <v>505</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8064,13 +8064,13 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>nrc2001</t>
+          <t>nrc2021</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -8080,25 +8080,25 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>505</v>
+        <v>464</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>@book{nrc2001,</t>
+          <t>@book{nrc2021,</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>nrc2001</t>
+          <t>nrc2021</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8108,19 +8108,19 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>512</v>
+        <v>562</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>location  = {Washington, DC},</t>
+          <t>@book{nrc2021,</t>
         </is>
       </c>
       <c r="F262" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="263">
@@ -8136,11 +8136,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="264">
@@ -8164,11 +8164,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>562</v>
+        <v>498</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8176,31 +8176,31 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>nrc2021</t>
+          <t>pahlow2003microbiology</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>incollection</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>440</v>
+        <v>254</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>@book{nrc2021,</t>
+          <t>year = {2023}</t>
         </is>
       </c>
       <c r="F265" t="n">
@@ -8210,25 +8210,25 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>nrc2021</t>
+          <t>pahlow2003microbiology</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>incollection</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>498</v>
+        <v>352</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>@book{nrc2021,</t>
+          <t>year = {2023}</t>
         </is>
       </c>
       <c r="F266" t="n">
@@ -8238,25 +8238,25 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>nrc2021</t>
+          <t>pahlow2003microbiology</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>incollection</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>503</v>
+        <v>230</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>doi       = {10.1038/216164a0}</t>
+          <t>year = {2023}</t>
         </is>
       </c>
       <c r="F267" t="n">
@@ -8276,11 +8276,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -8304,11 +8304,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>352</v>
+        <v>274</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -8322,81 +8322,81 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>pahlow2003microbiology</t>
+          <t>parton1987analysis</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>incollection</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>230</v>
+        <v>11</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>year = {2023}</t>
+          <t>@article{parton1987analysis,</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>pahlow2003microbiology</t>
+          <t>parton1987analysis</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>incollection</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>288</v>
+        <v>607</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>year = {2023}</t>
+          <t>publisher={American Society of Agricultural and Biological Engineers}</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>pahlow2003microbiology</t>
+          <t>reed2015</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>incollection</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>274</v>
+        <v>432</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>year = {2023}</t>
+          <t>doi = {10.3168/jds.S0022-0302(05)73058-7}</t>
         </is>
       </c>
       <c r="F272" t="n">
@@ -8406,7 +8406,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>parton1987analysis</t>
+          <t>reed2015</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -8420,21 +8420,21 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>11</v>
+        <v>530</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>@article{parton1987analysis,</t>
+          <t>doi = {10.3168/jds.S0022-0302(05)73058-7}</t>
         </is>
       </c>
       <c r="F273" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>parton1987analysis</t>
+          <t>reed2015</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -8444,19 +8444,19 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>607</v>
+        <v>408</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>publisher={American Society of Agricultural and Biological Engineers}</t>
+          <t>doi = {10.3168/jds.S0022-0302(05)73058-7}</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="275">
@@ -8472,11 +8472,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>432</v>
+        <v>466</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -8500,11 +8500,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>530</v>
+        <v>469</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -8518,85 +8518,85 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>reed2015</t>
+          <t>reuven2017</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>book</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>408</v>
+        <v>532</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>doi = {10.3168/jds.S0022-0302(05)73058-7}</t>
+          <t>@book{reuven2017,</t>
         </is>
       </c>
       <c r="F277" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>reed2015</t>
+          <t>reuven2017</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>book</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>466</v>
+        <v>630</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>doi = {10.3168/jds.S0022-0302(05)73058-7}</t>
+          <t>@book{reuven2017,</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>reed2015</t>
+          <t>reuven2017</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>book</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>469</v>
+        <v>508</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>doi = {10.3168/jds.S0022-0302(05)73058-7}</t>
+          <t>@book{reuven2017,</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="280">
@@ -8612,11 +8612,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>532</v>
+        <v>566</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -8624,31 +8624,31 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>reuven2017</t>
+          <t>vadas2007</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>630</v>
+        <v>443</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>@book{reuven2017,</t>
+          <t>pages = {3025--3035}</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -8658,25 +8658,25 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>reuven2017</t>
+          <t>vadas2007</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>508</v>
+        <v>541</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>@book{reuven2017,</t>
+          <t>pages = {3025--3035}</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -8686,25 +8686,25 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>reuven2017</t>
+          <t>vadas2007</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>566</v>
+        <v>419</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>@book{reuven2017,</t>
+          <t>pages = {3025--3035}</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -8714,25 +8714,25 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>reuven2017</t>
+          <t>vadas2007</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>587</v>
+        <v>477</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>pages   = {3246-3267}</t>
+          <t>pages = {3025--3035}</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -8752,11 +8752,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>443</v>
+        <v>480</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -8770,63 +8770,63 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>vadas2007</t>
+          <t>wallaceDMI</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>541</v>
+        <v>1</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>pages = {3025--3035}</t>
+          <t>@misc{wallaceDMI,</t>
         </is>
       </c>
       <c r="F286" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>vadas2007</t>
+          <t>wallaceDMI</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>419</v>
+        <v>735</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>pages = {3025--3035}</t>
+          <t>note      = {\url{http://ww2.arb.ca.gov/sites/default/files/classic/research/apr/past/16rd002.pdf}},</t>
         </is>
       </c>
       <c r="F287" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>vadas2007</t>
+          <t>wilkerson1997prediction</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8836,25 +8836,25 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>477</v>
+        <v>14</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>pages = {3025--3035}</t>
+          <t>url          = {https://www.dcrcouncil.org/protocols/}</t>
         </is>
       </c>
       <c r="F288" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>vadas2007</t>
+          <t>wilkerson1997prediction</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8868,39 +8868,39 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>480</v>
+        <v>16</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>pages = {3025--3035}</t>
+          <t>url          = {https://www.dcrcouncil.org/protocols/}</t>
         </is>
       </c>
       <c r="F289" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>wallaceDMI</t>
+          <t>williams1978optimal</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>techreport</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>@misc{wallaceDMI,</t>
+          <t>@techreport{williams1978optimal,</t>
         </is>
       </c>
       <c r="F290" t="n">
@@ -8910,12 +8910,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>wallaceDMI</t>
+          <t>williams1978optimal</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>techreport</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8924,11 +8924,11 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>735</v>
+        <v>631</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>note      = {\url{http://ww2.arb.ca.gov/sites/default/files/classic/research/apr/past/16rd002.pdf}},</t>
+          <t>publisher={The Royal Society London}</t>
         </is>
       </c>
       <c r="F291" t="n">
@@ -8938,7 +8938,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>wilkerson1997prediction</t>
+          <t>wiltbank2016</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8952,21 +8952,21 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>14</v>
+        <v>478</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>url          = {https://www.dcrcouncil.org/protocols/}</t>
+          <t>@article{wiltbank2016,</t>
         </is>
       </c>
       <c r="F292" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>wilkerson1997prediction</t>
+          <t>wiltbank2016</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8976,75 +8976,75 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>16</v>
+        <v>576</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>url          = {https://www.dcrcouncil.org/protocols/}</t>
+          <t>@article{wiltbank2016,</t>
         </is>
       </c>
       <c r="F293" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>williams1978optimal</t>
+          <t>wiltbank2016</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>techreport</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>31</v>
+        <v>454</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>@techreport{williams1978optimal,</t>
+          <t>@article{wiltbank2016,</t>
         </is>
       </c>
       <c r="F294" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>williams1978optimal</t>
+          <t>wiltbank2016</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>techreport</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>631</v>
+        <v>512</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>publisher={The Royal Society London}</t>
+          <t>@article{wiltbank2016,</t>
         </is>
       </c>
       <c r="F295" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="296">
@@ -9060,135 +9060,23 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>478</v>
+        <v>521</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>@article{wiltbank2016,</t>
+          <t>address   = {Washington, D.C.}</t>
         </is>
       </c>
       <c r="F296" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>wiltbank2016</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>article</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>resources/crop_and_soil.bib</t>
-        </is>
-      </c>
-      <c r="D297" t="n">
-        <v>576</v>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>@article{wiltbank2016,</t>
-        </is>
-      </c>
-      <c r="F297" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>wiltbank2016</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>article</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>resources/feed_storage.bib</t>
-        </is>
-      </c>
-      <c r="D298" t="n">
-        <v>454</v>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>@article{wiltbank2016,</t>
-        </is>
-      </c>
-      <c r="F298" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>wiltbank2016</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>article</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>resources/manure.bib</t>
-        </is>
-      </c>
-      <c r="D299" t="n">
-        <v>512</v>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>@article{wiltbank2016,</t>
-        </is>
-      </c>
-      <c r="F299" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>wiltbank2016</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>article</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>rufas.bib</t>
-        </is>
-      </c>
-      <c r="D300" t="n">
-        <v>521</v>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>address   = {Washington, D.C.}</t>
-        </is>
-      </c>
-      <c r="F300" t="n">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F300"/>
+  <autoFilter ref="A1:F296"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9471,11 +9359,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>resources/animal.bib; resources/crop_and_soil.bib; resources/feed_storage.bib; resources/manure.bib; rufas.bib</t>
+          <t>resources/animal.bib; resources/crop_and_soil.bib; resources/feed_storage.bib; resources/manure.bib</t>
         </is>
       </c>
     </row>
@@ -10101,11 +9989,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>resources/animal.bib; resources/crop_and_soil.bib; resources/feed_storage.bib; resources/manure.bib; rufas.bib</t>
+          <t>resources/animal.bib; resources/crop_and_soil.bib; resources/feed_storage.bib; resources/manure.bib</t>
         </is>
       </c>
     </row>
@@ -10116,11 +10004,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>resources/animal.bib; resources/crop_and_soil.bib; resources/feed_storage.bib; resources/manure.bib; rufas.bib</t>
+          <t>resources/animal.bib; resources/crop_and_soil.bib; resources/feed_storage.bib; resources/manure.bib</t>
         </is>
       </c>
     </row>
@@ -10176,11 +10064,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>resources/animal.bib; resources/crop_and_soil.bib; resources/feed_storage.bib; resources/manure.bib; rufas.bib</t>
+          <t>resources/animal.bib; resources/crop_and_soil.bib; resources/feed_storage.bib; resources/manure.bib</t>
         </is>
       </c>
     </row>
@@ -10271,13 +10159,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10302,8 +10190,108 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LASTNAME_YEARa</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>212</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>If there are 2 articles with the same author and same year, add the recommended "a" or "b" (e.g. ```bibtex @LASTNAME_YEARa vs @LASTNAME_YEARb```) as they are referenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LASTNAME_YEARb</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>212</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>If there are 2 articles with the same author and same year, add the recommended "a" or "b" (e.g. ```bibtex @LASTNAME_YEARa vs @LASTNAME_YEARb```) as they are referenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>183</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>@article{LASTNAME_YEAR,</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>194</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>@book{LASTNAME_YEAR,</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>204</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>@online{quarto2024,</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A1:D6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10345,7 +10333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10391,173 +10379,263 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Animal module icon</t>
+          <t>AN.NRC.2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>resources/animal.png</t>
+          <t>#eq-an-nrc-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>internal-file</t>
+          <t>anchor</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>127</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
+          <t>See [AN.NRC.2](#eq-an-nrc-2)&lt;!-- @eq-an-nrc-2 --&gt;.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>AN.NRC.2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>#eq-an-nrc-50</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>See [AN.NRC.2](#eq-an-nrc-50)&lt;!-- @eq-an-nrc-=50 --&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Animal module icon</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>resources/animal.png</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>internal-file</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>![Animal module icon](resources/animal.png){width=35%}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Animal module icon</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>resources/animal.png</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>internal-file</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>example_structures.qmd</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>17</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E5" t="n">
+        <v>77</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Animal module icon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>resources/animal.png</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>internal-file</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>88</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
         <is>
           <t>resources/manure.png</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>internal-file</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>manure.qmd</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E7" t="n">
         <v>4</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>![](resources/manure.png){width=140px}</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
         <is>
           <t>resources/manure.png</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>internal-file</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>manure.qmd</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E8" t="n">
         <v>16</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>![](resources/manure.png){width=50%}</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
         <is>
           <t>resources/rufas.png</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>internal-file</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>index.qmd</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E9" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>![](resources/rufas.png){width=90}</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>energykey</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>energy</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>example_structures.qmd</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>48</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E10" t="n">
+        <v>219</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>calculation, please refer to the [energykey](energy requirements key).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:F10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10623,7 +10701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10688,11 +10766,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
+          <t>![Animal module icon](resources/animal.png){width=35%}</t>
         </is>
       </c>
     </row>
@@ -10718,7 +10796,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10727,10 +10805,14 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Animal module icon</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>resources/manure.png</t>
+          <t>resources/animal.png</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -10740,15 +10822,15 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>manure.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>![](resources/manure.png){width=140px}</t>
+          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
         </is>
       </c>
     </row>
@@ -10770,11 +10852,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>![](resources/manure.png){width=50%}</t>
+          <t>![](resources/manure.png){width=140px}</t>
         </is>
       </c>
     </row>
@@ -10782,30 +10864,56 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
+          <t>resources/manure.png</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>internal-file</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>manure.qmd</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>![](resources/manure.png){width=50%}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>resources/rufas.png</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>internal-file</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>index.qmd</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>![](resources/rufas.png){width=90}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10816,15 +10924,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10859,8 +10967,68 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AN.NRC.2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>#eq-an-nrc-2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>127</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>See [AN.NRC.2](#eq-an-nrc-2)&lt;!-- @eq-an-nrc-2 --&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AN.NRC.2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>#eq-an-nrc-50</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>See [AN.NRC.2](#eq-an-nrc-50)&lt;!-- @eq-an-nrc-=50 --&gt;.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10936,7 +11104,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>219</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11011,7 +11179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11019,7 +11187,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="73" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11071,7 +11239,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>290</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -11101,7 +11269,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>274</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -11131,7 +11299,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>125</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -11161,7 +11329,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>257</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -11191,7 +11359,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>278</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -11221,7 +11389,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>282</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -11251,7 +11419,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>286</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -11267,7 +11435,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>eq-an-nrc-6</t>
+          <t>eq-an-nrc-50</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -11277,11 +11445,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -11290,7 +11458,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>$$ {#eq-an-nrc-6}</t>
+          <t>$$ {#eq-an-nrc-50}</t>
         </is>
       </c>
     </row>
@@ -11307,11 +11475,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>example_structures.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>35</v>
+        <v>294</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -11341,7 +11509,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>267</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -11371,7 +11539,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>56</v>
+        <v>227</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -11401,7 +11569,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>75</v>
+        <v>246</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -11431,7 +11599,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>231</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -11461,7 +11629,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>237</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -11491,7 +11659,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>106</v>
+        <v>277</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -11517,11 +11685,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -11551,7 +11719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -11581,7 +11749,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -11597,7 +11765,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tbl-animal-inputs</t>
+          <t>tbl-animal-grp-inputs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11611,7 +11779,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -11620,14 +11788,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+          <t>: User inputs in the animal input file that influence pen grouping. The user must define at least 3 pens and for each pen, key inputs are outlined here. {#tbl-animal-grp-inputs}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tbl-animal-inputs</t>
+          <t>tbl-animal-grp-inputs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11637,11 +11805,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>example_structures.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25</v>
+        <v>205</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -11650,42 +11818,162 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+          <t>: Summary of animal types and their grouping included in this module. {#tbl-animal-grp-inputs}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>tbl-animal-herd-inputs</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>89</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>: User inputs in the animal input file that influence the generation of the Animal Population (pre-animal-population). The inputs of this table are found in the Herd Initialization Section. {#tbl-animal-herd-inputs}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>tbl-animal-inputs</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Table</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>98</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>tbl-animal-inputs</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>114</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>tbl-animal-inputs</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>manure.qmd</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D25" t="n">
         <v>26</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>attribute-id</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>: Example animal inputs {#tbl-animal-inputs}</t>
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>tbl-animal-simulation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>72</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>: Overview of the distinct phases by which animals are created and introduced to the herd. {#tbl-animal-simulation}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F22"/>
+  <autoFilter ref="A1:F26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11844,7 +12132,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>272</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -11889,7 +12177,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>26</v>
+        <v>276</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -11934,7 +12222,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>280</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -11979,7 +12267,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -12024,7 +12312,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>38</v>
+        <v>288</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -12069,7 +12357,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>42</v>
+        <v>292</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -12114,7 +12402,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -12130,17 +12418,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>eq-an-nrc-6</t>
+          <t>eq-an-nrc-50</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AN.NRC.6</t>
+          <t>AN.NRC.50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AN.NRC.6</t>
+          <t>AN.NRC.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -12159,11 +12447,11 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>33</v>
+        <v>129</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.6)}</t>
+          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.50)}</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -12200,7 +12488,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>54</v>
+        <v>225</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -12241,7 +12529,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>58</v>
+        <v>229</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -12282,7 +12570,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>64</v>
+        <v>235</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -12323,7 +12611,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>73</v>
+        <v>244</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -12368,7 +12656,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>84</v>
+        <v>255</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -12409,7 +12697,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>94</v>
+        <v>265</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -12450,7 +12738,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>100</v>
+        <v>271</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -12535,7 +12823,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>54</v>
+        <v>225</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -12565,7 +12853,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>58</v>
+        <v>229</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -12595,7 +12883,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>64</v>
+        <v>235</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -12625,7 +12913,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>244</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -12655,7 +12943,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>94</v>
+        <v>265</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -12685,7 +12973,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>100</v>
+        <v>271</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -12781,7 +13069,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>84</v>
+        <v>255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12806,7 +13094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12872,7 +13160,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>272</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -12905,7 +13193,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -12938,7 +13226,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>84</v>
+        <v>255</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -12954,74 +13242,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AN.NRC.6</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>eq-an-nrc-6</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>animal.qmd</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>42</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.6)}</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>$$</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AN.NRC.6</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>eq-an-nrc-6</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>example_structures.qmd</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>33</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CBW = MW * 0.06275 \qquad \text{(AN.NRC.6)}</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>$$</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13032,7 +13254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13072,23 +13294,8 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AN.NRC.6</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>animal.qmd; example_structures.qmd</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C3"/>
+  <autoFilter ref="A1:C2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13099,7 +13306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13145,7 +13352,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eq-an-nrc-2</t>
+          <t>eq-an-nrc-</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -13155,11 +13362,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -13168,7 +13375,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>See @eq-an-nrc-2.</t>
+          <t>See [AN.NRC.2](#eq-an-nrc-50)&lt;!-- @eq-an-nrc-=50 --&gt;.</t>
         </is>
       </c>
     </row>
@@ -13185,11 +13392,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>example_structures.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>37</v>
+        <v>296</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -13205,7 +13412,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>eq-an-nrc-2-tagged</t>
+          <t>eq-an-nrc-2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -13219,7 +13426,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -13228,14 +13435,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>See @eq-an-nrc-2-tagged.</t>
+          <t>See [AN.NRC.2](#eq-an-nrc-2)&lt;!-- @eq-an-nrc-2 --&gt;.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>eq-energy</t>
+          <t>eq-an-nrc-2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -13249,51 +13456,141 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>@id</t>
+          <t>(#id)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>See Equation @eq-energy.</t>
+          <t>See [AN.NRC.2](#eq-an-nrc-2)&lt;!-- @eq-an-nrc-2 --&gt;.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>eq-an-nrc-2-tagged</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>259</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>@id</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>See @eq-an-nrc-2-tagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>133</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>(#id)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>See [AN.NRC.2](#eq-an-nrc-50)&lt;!-- @eq-an-nrc-=50 --&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>eq-energy</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>269</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>@id</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>See Equation @eq-energy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>eq-nrc-cbw</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>example_structures.qmd</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>70</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D9" t="n">
+        <v>241</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>@id</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>@eq-nrc-cbw may be visually improved by using the `\times` LaTeX</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13307,12 +13604,12 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="73" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -13370,7 +13667,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>274</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -13403,7 +13700,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>125</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -13422,21 +13719,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>eq-an-nrc-6</t>
+          <t>fig-animal-icon</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -13445,7 +13742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>$$ {#eq-an-nrc-6}</t>
+          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -13455,12 +13752,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>eq-an-nrc-6</t>
+          <t>fig-animal-icon</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13469,7 +13766,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -13478,7 +13775,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>$$ {#eq-an-nrc-6}</t>
+          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -13488,12 +13785,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fig-animal-icon</t>
+          <t>tbl-animal-grp-inputs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -13502,7 +13799,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>178</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -13511,7 +13808,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
+          <t>: User inputs in the animal input file that influence pen grouping. The user must define at least 3 pens and for each pen, key inputs are outlined here. {#tbl-animal-grp-inputs}</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -13521,21 +13818,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fig-animal-icon</t>
+          <t>tbl-animal-grp-inputs</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>example_structures.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -13544,7 +13841,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
+          <t>: Summary of animal types and their grouping included in this module. {#tbl-animal-grp-inputs}</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -13564,11 +13861,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -13601,7 +13898,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -13665,10 +13962,10 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13716,12 +14013,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>eq-an-nrc-6</t>
+          <t>fig-animal-icon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -13729,19 +14026,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>animal.qmd; example_structures.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fig-animal-icon</t>
+          <t>tbl-animal-grp-inputs</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -13749,7 +14046,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>animal.qmd; example_structures.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
     </row>
@@ -13769,7 +14066,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>animal.qmd; example_structures.qmd; manure.qmd</t>
+          <t>example_structures.qmd; manure.qmd</t>
         </is>
       </c>
     </row>
@@ -13785,15 +14082,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13828,8 +14125,38 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>eq-an-nrc-</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>133</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>@id</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>See [AN.NRC.2](#eq-an-nrc-50)&lt;!-- @eq-an-nrc-=50 --&gt;.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13840,7 +14167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13848,7 +14175,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="73" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13900,7 +14227,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>290</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -13930,7 +14257,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>278</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -13960,7 +14287,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>282</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -13990,7 +14317,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36</v>
+        <v>286</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -14020,7 +14347,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>44</v>
+        <v>294</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -14036,7 +14363,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>eq-an-nrc-6</t>
+          <t>eq-nrc-cbw-times</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -14050,7 +14377,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>246</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -14059,14 +14386,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>$$ {#eq-an-nrc-6}</t>
+          <t>$$ {#eq-nrc-cbw-times}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>eq-nrc-cbw-times</t>
+          <t>eq-nrc-cw</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -14080,7 +14407,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>75</v>
+        <v>231</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -14089,14 +14416,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>$$ {#eq-nrc-cbw-times}</t>
+          <t>$$ {#eq-nrc-cw}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>eq-nrc-cw</t>
+          <t>eq-nrc-ne-maint</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -14110,7 +14437,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
+        <v>237</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -14119,14 +14446,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>$$ {#eq-nrc-cw}</t>
+          <t>$$ {#eq-nrc-ne-maint}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>eq-nrc-ne-maint</t>
+          <t>eq-nutrient-proportion</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -14140,7 +14467,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>66</v>
+        <v>277</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -14149,19 +14476,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>$$ {#eq-nrc-ne-maint}</t>
+          <t>$$ {#eq-nutrient-proportion}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>eq-nutrient-proportion</t>
+          <t>fig-animal-icon</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -14170,7 +14497,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -14179,7 +14506,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>$$ {#eq-nutrient-proportion}</t>
+          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
         </is>
       </c>
     </row>
@@ -14196,11 +14523,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>animal.qmd</t>
+          <t>example_structures.qmd</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -14216,12 +14543,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fig-animal-icon</t>
+          <t>sec-nrc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -14230,7 +14557,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>216</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -14239,28 +14566,28 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>![Animal module icon](resources/animal.png){#fig-animal-icon width=35%}</t>
+          <t>## Nutrient Requirements of Dairy Cattle (NRC) {#sec-nrc}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sec-nrc</t>
+          <t>tbl-animal-grp-inputs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Section</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>example_structures.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -14269,14 +14596,14 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>## Nutrient Requirements of Dairy Cattle (NRC) {#sec-nrc}</t>
+          <t>: User inputs in the animal input file that influence pen grouping. The user must define at least 3 pens and for each pen, key inputs are outlined here. {#tbl-animal-grp-inputs}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tbl-animal-inputs</t>
+          <t>tbl-animal-grp-inputs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -14290,7 +14617,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>205</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -14299,14 +14626,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+          <t>: Summary of animal types and their grouping included in this module. {#tbl-animal-grp-inputs}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tbl-animal-inputs</t>
+          <t>tbl-animal-herd-inputs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -14316,11 +14643,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>example_structures.qmd</t>
+          <t>animal.qmd</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -14329,7 +14656,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+          <t>: User inputs in the animal input file that influence the generation of the Animal Population (pre-animal-population). The inputs of this table are found in the Herd Initialization Section. {#tbl-animal-herd-inputs}</t>
         </is>
       </c>
     </row>
@@ -14346,25 +14673,115 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>98</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tbl-animal-inputs</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>114</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>: Example animal inputs {#tbl-animal-inputs}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tbl-animal-inputs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>manure.qmd</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D19" t="n">
         <v>26</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>attribute-id</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>: Example animal inputs {#tbl-animal-inputs}</t>
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tbl-animal-simulation</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>72</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>attribute-id</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>: Overview of the distinct phases by which animals are created and introduced to the herd. {#tbl-animal-simulation}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F17"/>
+  <autoFilter ref="A1:F20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16515,7 +16932,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Li2022</t>
+          <t>Li2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -16525,15 +16942,15 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>565</v>
+        <v>523</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>pages   = {2681-2693}</t>
+          <t>@article{Li2023,</t>
         </is>
       </c>
     </row>
@@ -16550,11 +16967,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>523</v>
+        <v>621</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -16575,11 +16992,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>621</v>
+        <v>499</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -16600,11 +17017,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>499</v>
+        <v>557</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -16625,22 +17042,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>557</v>
+        <v>576</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>@article{Li2023,</t>
+          <t>pages   = {7525–7538}</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Li2023</t>
+          <t>Li_2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -16654,11 +17071,11 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>pages   = {7525–7538}</t>
+          <t>pages   = {2681-2693}</t>
         </is>
       </c>
     </row>
@@ -20915,7 +21332,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>nrc2001</t>
+          <t>nrc2021</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20925,15 +21342,15 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>rufas.bib</t>
+          <t>resources/animal.bib</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>512</v>
+        <v>464</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>location  = {Washington, DC},</t>
+          <t>@book{nrc2021,</t>
         </is>
       </c>
     </row>
@@ -20950,11 +21367,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>resources/animal.bib</t>
+          <t>resources/crop_and_soil.bib</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>464</v>
+        <v>562</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -20975,11 +21392,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>resources/crop_and_soil.bib</t>
+          <t>resources/feed_storage.bib</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>562</v>
+        <v>440</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -21000,11 +21417,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>resources/feed_storage.bib</t>
+          <t>resources/manure.bib</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -21015,7 +21432,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>nrc2021</t>
+          <t>nrc_2001</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21025,22 +21442,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>resources/manure.bib</t>
+          <t>rufas.bib</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>@book{nrc2021,</t>
+          <t>location  = {Washington, DC},</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>nrc2021</t>
+          <t>nrc_2021</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21465,7 +21882,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>reuven2017</t>
+          <t>reuven_2017</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -21899,13 +22316,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21930,8 +22347,208 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LASTNAME_YEARa</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>212</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>If there are 2 articles with the same author and same year, add the recommended "a" or "b" (e.g. ```bibtex @LASTNAME_YEARa vs @LASTNAME_YEARb```) as they are referenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LASTNAME_YEARb</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>212</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>If there are 2 articles with the same author and same year, add the recommended "a" or "b" (e.g. ```bibtex @LASTNAME_YEARa vs @LASTNAME_YEARb```) as they are referenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Li_2022</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>230</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>The diet recipes in RuFaS are either formulated through least-cost formulation [@Li_2022] or provided by the user for each of 4 animal categories (calves, growing heifers, dry and close-up cows, and lactating cows). The composition of the available feeds are provided by a feed library that was adapted from the [@nrc_2021]. The amount of feed required by the farm is tracked by pen and multiple pens of each animal category can be simulated; however, at this time, the RuFaS model can only accept 1 user-defined diet per animal category even if there are multiple simulated pens for that animal category.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>183</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>@article{LASTNAME_YEAR,</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>194</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>@book{LASTNAME_YEAR,</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>nrc_2001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>248</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Below are the calculations utilized based on the energy and nutrient requirements of dairy cattle as reported by the NRC and more recently the NASEM @nrc_2001, @nrc_2021.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>nrc_2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>230</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>The diet recipes in RuFaS are either formulated through least-cost formulation [@Li_2022] or provided by the user for each of 4 animal categories (calves, growing heifers, dry and close-up cows, and lactating cows). The composition of the available feeds are provided by a feed library that was adapted from the [@nrc_2021]. The amount of feed required by the farm is tracked by pen and multiple pens of each animal category can be simulated; however, at this time, the RuFaS model can only accept 1 user-defined diet per animal category even if there are multiple simulated pens for that animal category.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>nrc_2021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>248</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Below are the calculations utilized based on the energy and nutrient requirements of dairy cattle as reported by the NRC and more recently the NASEM @nrc_2001, @nrc_2021.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>example_structures.qmd</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>204</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>@online{quarto2024,</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>reuven_2017</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>animal.qmd</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The life cycle module represents the variation in animal performance through the use of Monte Carlo Simulation methods [@reuven_2017]. Monte Carlo simulation relies on random draws from probability distributions rather than assigning fixed values. In this model, two main strategies are used:</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A1:D11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>